--- a/CrCraft队伍注册表.xlsx
+++ b/CrCraft队伍注册表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>注册时间</t>
   </si>
@@ -56,121 +56,40 @@
     <t>加入时间</t>
   </si>
   <si>
-    <t>xiaomin</t>
+    <t>Arknights</t>
+  </si>
+  <si>
+    <t>深蓝</t>
+  </si>
+  <si>
+    <t>Gypsophila</t>
   </si>
   <si>
     <t>加粗表示队长</t>
   </si>
   <si>
-    <t>XXX</t>
+    <t>Xbcmzr</t>
   </si>
   <si>
     <t>下划线表示副队长或管理员</t>
   </si>
   <si>
-    <t>cgh</t>
+    <t>starry</t>
   </si>
   <si>
     <t>删除线表示玩家被此队伍拉黑</t>
   </si>
   <si>
-    <t>blue_fish233</t>
+    <t>白给少年团</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>BYyihan</t>
   </si>
   <si>
     <t>默认加入条件：管理员批准</t>
-  </si>
-  <si>
-    <t>Verebalize_</t>
-  </si>
-  <si>
-    <t>HUMIANTY</t>
-  </si>
-  <si>
-    <t>QSWY_MC</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>littlefish1688</t>
-  </si>
-  <si>
-    <t>Steve</t>
-  </si>
-  <si>
-    <t>lhl2</t>
-  </si>
-  <si>
-    <t>CXM</t>
-  </si>
-  <si>
-    <t>STAR</t>
-  </si>
-  <si>
-    <t>青</t>
-  </si>
-  <si>
-    <t>无需批准</t>
-  </si>
-  <si>
-    <t>KAMI</t>
-  </si>
-  <si>
-    <t>0526lhm</t>
-  </si>
-  <si>
-    <t>andy27</t>
-  </si>
-  <si>
-    <t>happypig</t>
-  </si>
-  <si>
-    <t>stiens_</t>
-  </si>
-  <si>
-    <t>xhf</t>
-  </si>
-  <si>
-    <t>zzz</t>
-  </si>
-  <si>
-    <t>partyking1145</t>
-  </si>
-  <si>
-    <t>0325491</t>
-  </si>
-  <si>
-    <t>Xuan_Air</t>
-  </si>
-  <si>
-    <t>Press_on</t>
-  </si>
-  <si>
-    <t>aKoishi</t>
-  </si>
-  <si>
-    <t>Arknights</t>
-  </si>
-  <si>
-    <t>深蓝</t>
-  </si>
-  <si>
-    <t>Gypsophila</t>
-  </si>
-  <si>
-    <t>Xbcmzr</t>
-  </si>
-  <si>
-    <t>starry</t>
-  </si>
-  <si>
-    <t>白给少年团</t>
-  </si>
-  <si>
-    <t>绿</t>
-  </si>
-  <si>
-    <t>BYyihan</t>
   </si>
   <si>
     <t>byfree</t>
@@ -274,7 +193,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -282,14 +201,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -297,19 +209,26 @@
       <b/>
       <u/>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -317,14 +236,7 @@
       <b/>
       <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -480,18 +392,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -827,67 +733,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -902,77 +811,74 @@
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -989,138 +895,108 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1488,853 +1364,537 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3</v>
+      </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="7" t="s">
-        <v>9</v>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="H2" s="4">
-        <v>920634333</v>
-      </c>
-      <c r="I2" s="8"/>
+        <v>3486811922</v>
+      </c>
+      <c r="I2" s="6"/>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="9" t="s">
-        <v>11</v>
+      <c r="G3" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="H3" s="4">
-        <v>920634333</v>
-      </c>
-      <c r="I3" s="8"/>
+        <v>985304787</v>
+      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="10" t="s">
-        <v>13</v>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="H4" s="4">
-        <v>2336143095</v>
-      </c>
-      <c r="I4" s="8"/>
+        <v>3486811922</v>
+      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2382134650</v>
-      </c>
-      <c r="I5" s="8"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10">
+        <v>4</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1765654884</v>
+      </c>
+      <c r="I5" s="12"/>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2020599174</v>
-      </c>
-      <c r="I6" s="8"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="10">
+        <v>2667055602</v>
+      </c>
+      <c r="I6" s="12"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4">
-        <v>3886693387</v>
-      </c>
-      <c r="I7" s="8"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1409004244</v>
+      </c>
+      <c r="I7" s="12"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="4">
-        <v>2735048086</v>
-      </c>
-      <c r="I8" s="8"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="17">
+        <v>758737003</v>
+      </c>
+      <c r="I8" s="17"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="4">
-        <v>2279319577</v>
-      </c>
-      <c r="I9" s="8"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="17">
+        <v>1983383774</v>
+      </c>
+      <c r="I9" s="17"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2825133848</v>
-      </c>
-      <c r="I10" s="8"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="17">
+        <v>2705525405</v>
+      </c>
+      <c r="I10" s="17"/>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="4">
-        <v>2133498209</v>
-      </c>
-      <c r="I11" s="8"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="17">
+        <v>7</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="17">
+        <v>2408450176</v>
+      </c>
+      <c r="I11" s="17"/>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="4">
-        <v>3012312191</v>
-      </c>
-      <c r="I12" s="8"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="17">
+        <v>2307916860</v>
+      </c>
+      <c r="I12" s="17"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="6">
-        <v>22</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="4">
-        <v>3264155797</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="11"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="17">
+        <v>2949047592</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="4">
-        <v>3505751672</v>
-      </c>
-      <c r="I14" s="8"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="17">
+        <v>354672662</v>
+      </c>
+      <c r="I14" s="21">
+        <v>46038</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="4">
-        <v>3490656940</v>
-      </c>
-      <c r="I15" s="8"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="23">
+        <v>3</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="23">
+        <v>3782933040</v>
+      </c>
+      <c r="I15" s="25"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1448998632</v>
-      </c>
-      <c r="I16" s="8"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="23">
+        <v>3950242464</v>
+      </c>
+      <c r="I16" s="25"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="4">
-        <v>2849206891</v>
-      </c>
-      <c r="I17" s="8"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="23">
+        <v>362273762</v>
+      </c>
+      <c r="I17" s="25"/>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="4">
-        <v>3570980865</v>
-      </c>
-      <c r="I18" s="8"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="28">
+        <v>3</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="28">
+        <v>2573888108</v>
+      </c>
+      <c r="I18" s="30"/>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="4">
-        <v>920634333</v>
-      </c>
-      <c r="I19" s="8"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="28">
+        <v>2573888108</v>
+      </c>
+      <c r="I19" s="30"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="4">
-        <v>3696490737</v>
-      </c>
-      <c r="I20" s="8"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="28">
+        <v>3626117581</v>
+      </c>
+      <c r="I20" s="30"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="4">
-        <v>2524546128</v>
-      </c>
-      <c r="I21" s="8"/>
+      <c r="A21" s="32">
+        <v>45891</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="33">
+        <v>4</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="33">
+        <v>1299972820</v>
+      </c>
+      <c r="I21" s="35">
+        <v>45892</v>
+      </c>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" s="4">
-        <v>3409188845</v>
-      </c>
-      <c r="I22" s="12">
-        <v>45894</v>
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="37">
+        <v>3973229304</v>
+      </c>
+      <c r="I22" s="35">
+        <v>45892</v>
       </c>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="4">
-        <v>1419555484</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="37">
+        <v>1691294516</v>
+      </c>
+      <c r="I23" s="35">
         <v>45893</v>
       </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="4">
-        <v>2133498209</v>
-      </c>
-      <c r="I24" s="12"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="33">
+        <v>3040913141</v>
+      </c>
+      <c r="I24" s="35">
+        <v>45893</v>
+      </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="14">
-        <v>3</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="14">
-        <v>3486811922</v>
-      </c>
-      <c r="I25" s="16"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="14">
-        <v>985304787</v>
-      </c>
-      <c r="I26" s="16"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="14">
-        <v>3486811922</v>
-      </c>
-      <c r="I27" s="16"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="20">
-        <v>4</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28" s="20">
-        <v>1765654884</v>
-      </c>
-      <c r="I28" s="22"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="18"/>
-      <c r="B29" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="20">
-        <v>2667055602</v>
-      </c>
-      <c r="I29" s="22"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" s="20">
-        <v>1409004244</v>
-      </c>
-      <c r="I30" s="22"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" s="27">
-        <v>758737003</v>
-      </c>
-      <c r="I31" s="27"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="27">
-        <v>1983383774</v>
-      </c>
-      <c r="I32" s="27"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="H33" s="27">
-        <v>2705525405</v>
-      </c>
-      <c r="I33" s="27"/>
+    <row r="33" spans="10:10">
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="25"/>
-      <c r="B34" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="27">
-        <v>7</v>
-      </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="27">
-        <v>2408450176</v>
-      </c>
-      <c r="I34" s="27"/>
+    <row r="34" spans="10:10">
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="27">
-        <v>2307916860</v>
-      </c>
-      <c r="I35" s="27"/>
+    <row r="35" spans="10:10">
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="H36" s="27">
-        <v>2949047592</v>
-      </c>
-      <c r="I36" s="27"/>
+    <row r="36" spans="10:10">
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="25"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H37" s="27">
-        <v>354672662</v>
-      </c>
-      <c r="I37" s="30">
-        <v>46038</v>
-      </c>
+    <row r="37" spans="10:10">
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="31"/>
-      <c r="B38" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="32">
-        <v>3</v>
-      </c>
-      <c r="F38" s="32"/>
-      <c r="G38" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="32">
-        <v>3782933040</v>
-      </c>
-      <c r="I38" s="34"/>
+    <row r="38" spans="10:10">
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="32">
-        <v>3950242464</v>
-      </c>
-      <c r="I39" s="34"/>
+    <row r="39" spans="10:10">
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="31"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="H40" s="32">
-        <v>362273762</v>
-      </c>
-      <c r="I40" s="34"/>
+    <row r="40" spans="10:10">
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="36"/>
-      <c r="B41" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="37">
-        <v>3</v>
-      </c>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="37">
-        <v>2573888108</v>
-      </c>
-      <c r="I41" s="39"/>
+    <row r="41" spans="10:10">
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H42" s="37">
-        <v>2573888108</v>
-      </c>
-      <c r="I42" s="39"/>
+    <row r="42" spans="10:10">
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="36"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="37">
-        <v>3626117581</v>
-      </c>
-      <c r="I43" s="39"/>
+    <row r="43" spans="10:10">
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="41">
-        <v>45891</v>
-      </c>
-      <c r="B44" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="E44" s="42">
-        <v>4</v>
-      </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H44" s="42">
-        <v>1299972820</v>
-      </c>
-      <c r="I44" s="44">
-        <v>45892</v>
-      </c>
+    <row r="44" spans="10:10">
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="H45" s="46">
-        <v>3973229304</v>
-      </c>
-      <c r="I45" s="44">
-        <v>45892</v>
-      </c>
+    <row r="45" spans="10:10">
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="41"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="H46" s="46">
-        <v>1691294516</v>
-      </c>
-      <c r="I46" s="44">
-        <v>45893</v>
-      </c>
+    <row r="46" spans="10:10">
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="H47" s="42">
-        <v>3040913141</v>
-      </c>
-      <c r="I47" s="44">
-        <v>45893</v>
-      </c>
+    <row r="47" spans="10:10">
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="10:10">
       <c r="J48" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="E21:E24"/>
   </mergeCells>
   <pageMargins left="0.74990626395218" right="0.74990626395218" top="0.999874956025852" bottom="0.999874956025852" header="0.499937478012926" footer="0.499937478012926"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="G21" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>